--- a/Book1.xlsx
+++ b/Book1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Liliu\Documents\MESIO_AB\BayesianProject\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{429D4915-E053-4239-AB3E-391479720724}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCE380A1-B0D6-4CB6-8EF2-E32EA6F789BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5760" yWindow="2916" windowWidth="17280" windowHeight="9960" firstSheet="6" activeTab="11" xr2:uid="{36094BA9-1D19-498E-884A-C6BBDC6CC8F7}"/>
   </bookViews>
@@ -1274,6 +1274,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F21B32B4-6411-497F-9F08-C33DC9AE09E2}">
   <dimension ref="A1:J11"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="11.109375" customWidth="1"/>
+    <col min="10" max="10" width="17.6640625" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="19.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
